--- a/reports/test-report-2026-04-15.xlsx
+++ b/reports/test-report-2026-04-15.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="568">
   <si>
     <t>Test Run Summary</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>15/4/2026, 3:30:35 pm</t>
+    <t>15/4/2026, 3:58:03 pm</t>
   </si>
   <si>
     <t>Total Tests</t>
@@ -43,7 +43,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>106.74s</t>
+    <t>120.47s</t>
   </si>
   <si>
     <t>Overall Status</t>
@@ -79,7 +79,7 @@
     <t>TC07 - Should show error when name is empty</t>
   </si>
   <si>
-    <t>10.37s</t>
+    <t>9.97s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -98,7 +98,7 @@
     <t>Camel login success</t>
   </si>
   <si>
-    <t>10.69s</t>
+    <t>11.69s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -113,7 +113,7 @@
     <t>TC08 - Should show error when name is too short</t>
   </si>
   <si>
-    <t>6.11s</t>
+    <t>6.63s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -149,7 +149,7 @@
     <t>TC10 - Should show error when email is too short (less than 5 characters)</t>
   </si>
   <si>
-    <t>8.41s</t>
+    <t>8.75s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -166,6 +166,9 @@
     <t>TC11 - Should show error when email format is invalid (missing domain)</t>
   </si>
   <si>
+    <t>7.71s</t>
+  </si>
+  <si>
     <t xml:space="preserve">Before Hooks
 Navigate to "/inquiry"
 Wait for load state "domcontentloaded"
@@ -180,7 +183,7 @@
     <t>TC12 - Should show error when email format is invalid (missing @)</t>
   </si>
   <si>
-    <t>6.17s</t>
+    <t>8.01s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -197,7 +200,7 @@
     <t>TC13 - Should show error when email format is invalid (missing username)</t>
   </si>
   <si>
-    <t>6.35s</t>
+    <t>8.05s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -217,7 +220,7 @@
     <t>TC14 - Should show error when mobile number is empty</t>
   </si>
   <si>
-    <t>7.26s</t>
+    <t>6.94s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -236,7 +239,7 @@
     <t>TC15 - Should show error when mobile number is too short</t>
   </si>
   <si>
-    <t>7.37s</t>
+    <t>9.34s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -253,29 +256,10 @@
 After Hooks</t>
   </si>
   <si>
-    <t>Enquiry Form - City Field Validation</t>
-  </si>
-  <si>
-    <t>TC17 - Should show error when city is empty</t>
-  </si>
-  <si>
-    <t>4.99s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Before Hooks
-Navigate to "/inquiry"
-Wait for load state "domcontentloaded"
-Click locator('input#city')
-Press "Tab" locator('input#city')
-Wait for selector locator('p.m-input-text__error[data-required="Enter the name of your city."]')
-Expect "toContain"
-After Hooks</t>
-  </si>
-  <si>
     <t>TC16 - Should show error when mobile number is too long</t>
   </si>
   <si>
-    <t>8.48s</t>
+    <t>8.16s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -292,13 +276,32 @@
 After Hooks</t>
   </si>
   <si>
+    <t>Enquiry Form - City Field Validation</t>
+  </si>
+  <si>
+    <t>TC17 - Should show error when city is empty</t>
+  </si>
+  <si>
+    <t>7.27s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Before Hooks
+Navigate to "/inquiry"
+Wait for load state "domcontentloaded"
+Click locator('input#city')
+Press "Tab" locator('input#city')
+Wait for selector locator('p.m-input-text__error[data-required="Enter the name of your city."]')
+Expect "toContain"
+After Hooks</t>
+  </si>
+  <si>
     <t>Enquiry Form - Message Field Validation</t>
   </si>
   <si>
     <t>TC18 - Should show error when message contains invalid characters</t>
   </si>
   <si>
-    <t>6.42s</t>
+    <t>7.17s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -318,7 +321,7 @@
     <t>TC19 - Should submit form successfully without message and file (optional fields)</t>
   </si>
   <si>
-    <t>13.38s</t>
+    <t>16.44s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -366,7 +369,7 @@
     <t>TC01 - Should fill and submit the complete enquiry form successfully</t>
   </si>
   <si>
-    <t>15.69s</t>
+    <t>18.02s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -418,7 +421,7 @@
     <t>TC02 - Should show auto-suggestion and first result should match typed city</t>
   </si>
   <si>
-    <t>7.30s</t>
+    <t>6.96s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -441,7 +444,7 @@
     <t>TC03 - Should open Business Unit dropdown and display all expected options</t>
   </si>
   <si>
-    <t>6.70s</t>
+    <t>7.89s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -470,7 +473,7 @@
     <t>TC04 - Should open Business Category dropdown and select an option</t>
   </si>
   <si>
-    <t>7.14s</t>
+    <t>7.06s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -491,7 +494,7 @@
     <t>TC05 - Should attach a valid file (png/jpg/docx) to the form</t>
   </si>
   <si>
-    <t>6.38s</t>
+    <t>6.21s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -510,7 +513,7 @@
     <t>TC07 - Should hide Business Category dropdown when Aerospace is selected as Business Unit</t>
   </si>
   <si>
-    <t>8.34s</t>
+    <t>8.27s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -525,13 +528,31 @@
 After Hooks</t>
   </si>
   <si>
+    <t>Negative Login Scenarios</t>
+  </si>
+  <si>
+    <t>#1 Unregistered or wrong credentials: "testuser@example.com"</t>
+  </si>
+  <si>
+    <t>4.64s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Before Hooks
+Open login page
+Enter email: testuser@example.com
+Enter password: Password123!
+Click login
+Verify validation message
+After Hooks</t>
+  </si>
+  <si>
     <t>Enquiry Form - Validation</t>
   </si>
   <si>
     <t>TC06 - Should not submit when all required fields are empty</t>
   </si>
   <si>
-    <t>6.19s</t>
+    <t>8.21s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -544,19 +565,16 @@
 After Hooks</t>
   </si>
   <si>
-    <t>Negative Login Scenarios</t>
-  </si>
-  <si>
-    <t>#1 Unregistered or wrong credentials: "testuser@example.com"</t>
-  </si>
-  <si>
-    <t>4.20s</t>
+    <t>#2 Invalid email format: "testgmailfd.com"</t>
+  </si>
+  <si>
+    <t>6.30s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
 Open login page
-Enter email: testuser@example.com
-Enter password: Password123!
+Enter email: testgmailfd.com
+Enter password: Password1@
 Click login
 Verify validation message
 After Hooks</t>
@@ -565,7 +583,7 @@
     <t>#5 Unregistered or wrong credentials: "test@gmai"</t>
   </si>
   <si>
-    <t>2.78s</t>
+    <t>4.47s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -577,25 +595,10 @@
 After Hooks</t>
   </si>
   <si>
-    <t>#2 Invalid email format: "testgmailfd.com"</t>
-  </si>
-  <si>
-    <t>2.99s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Before Hooks
-Open login page
-Enter email: testgmailfd.com
-Enter password: Password1@
-Click login
-Verify validation message
-After Hooks</t>
-  </si>
-  <si>
     <t>#6 Invalid email format: "123"</t>
   </si>
   <si>
-    <t>2.88s</t>
+    <t>3.79s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -610,7 +613,7 @@
     <t>#3 Invalid password for valid email: "test@test.com"</t>
   </si>
   <si>
-    <t>3.66s</t>
+    <t>3.61s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -625,7 +628,7 @@
     <t>#7 Unregistered or wrong credentials: "test.comgmail@"</t>
   </si>
   <si>
-    <t>2.92s</t>
+    <t>3.33s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -640,7 +643,7 @@
     <t>#4 Invalid email format: "@gmail.com"</t>
   </si>
   <si>
-    <t>3.33s</t>
+    <t>3.45s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -655,7 +658,7 @@
     <t>#8 Invalid email format: "OR 1=1 --"</t>
   </si>
   <si>
-    <t>3.29s</t>
+    <t>3.25s</t>
   </si>
   <si>
     <t xml:space="preserve">Before Hooks
@@ -796,6 +799,18 @@
     <t>Form NOT submitted — error: "Number must be 10 numbers"</t>
   </si>
   <si>
+    <t>TC16</t>
+  </si>
+  <si>
+    <t>Should show error when mobile number is too long</t>
+  </si>
+  <si>
+    <t>Mobile: "12345678901234567890" (20 digits - above max)</t>
+  </si>
+  <si>
+    <t>Form NOT submitted — error: "Number must be 10 digits."</t>
+  </si>
+  <si>
     <t>TC17</t>
   </si>
   <si>
@@ -808,18 +823,6 @@
     <t>Form NOT submitted — error: "Enter the name of your city."</t>
   </si>
   <si>
-    <t>TC16</t>
-  </si>
-  <si>
-    <t>Should show error when mobile number is too long</t>
-  </si>
-  <si>
-    <t>Mobile: "12345678901234567890" (20 digits - above max)</t>
-  </si>
-  <si>
-    <t>Form NOT submitted — error: "Number must be 10 digits."</t>
-  </si>
-  <si>
     <t>TC18</t>
   </si>
   <si>
@@ -898,6 +901,9 @@
     <t>Should hide Business Category dropdown when Aerospace is selected as Business Unit</t>
   </si>
   <si>
+    <t>TC21</t>
+  </si>
+  <si>
     <t>TC06</t>
   </si>
   <si>
@@ -910,9 +916,6 @@
     <t>Form NOT submitted — all required field errors shown</t>
   </si>
   <si>
-    <t>TC22</t>
-  </si>
-  <si>
     <t>TC23</t>
   </si>
   <si>
@@ -1644,6 +1647,722 @@
   </si>
   <si>
     <t xml:space="preserve">2026-04-15 15:30:35 [INFO] Log file for this run: C:\PlaywrightAutomation\logs\2026-04-15.log
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:10 [INFO] === TC07: Name empty validation ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:10 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:18 [INFO] Expected error to contain: "Enter your full name."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:18 [INFO] Actual error: "Enter your full name."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:19 [INFO] === TC08: Name too short validation ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:19 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:22 [INFO] === TC09: Email empty validation ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:22 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:25 [INFO] Filling Name: J
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:26 [INFO] Expected error to contain: "Name must be between 2-100 characters."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:26 [INFO] Actual error: "Name must be between 2-100 characters."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:26 [INFO] === TC10: Email too short validation ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:26 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:28 [INFO] Expected error to contain: "Enter your email address."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:28 [INFO] Actual error: "Enter your email address."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:30 [INFO] === TC11: Email invalid format - missing domain ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:30 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:33 [INFO] Filling Email: ab@c
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:34 [INFO] Expected error to contain: "Email address must be between 5-300 characters."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:34 [INFO] Actual error: "Email address must be between 5-300 characters."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:35 [INFO] Filling Email: johndoe@
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:36 [INFO] === TC12: Email invalid format - missing @ ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:36 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:36 [INFO] Expected error to contain: "Enter a valid email address."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:36 [INFO] Actual error: "Enter a valid email address."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:37 [INFO] === TC13: Email invalid format - missing username ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:37 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:41 [INFO] Filling Email: johndoe.com
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:43 [INFO] Expected error to contain: "Enter a valid email address."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:43 [INFO] Actual error: "Enter a valid email address."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:43 [INFO] Filling Email: @example.com
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:43 [INFO] === TC14: Mobile number empty ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:43 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:44 [INFO] Expected error to contain: "Enter a valid email address."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:44 [INFO] Actual error: "Enter a valid email address."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:46 [INFO] === TC15: Mobile number too short ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:46 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:48 [INFO] Selecting Country Code: +91
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:50 [INFO] Expected error to contain: "Enter your mobile number."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:50 [INFO] Actual error: "Enter your mobile number."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:50 [INFO] === TC16: Mobile number too long ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:50 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:52 [INFO] Selecting Country Code: +91
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:53 [INFO] Filling Mobile: 12345
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:54 [INFO] Expected error to contain: "Number must be 10 numbers"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:54 [INFO] Actual error: "Number must be 10 numbers"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:54 [INFO] === TC17: City empty validation ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:54 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:56 [INFO] Selecting Country Code: +91
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:57 [INFO] Filling Mobile: 12345678901234567890
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:58 [INFO] Expected error to contain: "Number must be 10 digits."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:58 [INFO] Actual error: "Number must be 10 digits."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:59 [INFO] === TC18: Message with invalid characters validation ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:56:59 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:01 [INFO] Expected error to contain: "Enter the name of your city."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:01 [INFO] Actual error: "Enter the name of your city."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:02 [INFO] === TC19: Submit form without optional fields ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:02 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:04 [INFO] Filling Message
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:05 [INFO] Expected error: "Message must be letters, numbers, spaces, and . - ! ( ) , &amp; and % characters are allowed."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:05 [INFO] Actual error: "Message must be letters, numbers, spaces, and . - ! ( ) , &amp; and % characters are allowed."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:07 [INFO] Filling Name: John Doe
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:07 [INFO] Filling Email: johndoe@example.com
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:07 [INFO] Selecting Country Code: +91
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:07 [INFO] === TC01: Full enquiry form submission ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:07 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:08 [INFO] Filling Mobile: 9876543210
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:09 [INFO] Typing city: "Mum" — expecting suggestion: "Mumbai"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:10 [INFO] First suggestion: "Mumbai"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:10 [INFO] Selecting Business Unit: Home Appliances
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:11 [INFO] Business Unit dropdown is open
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:12 [INFO] Filling Name: John Doe
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:13 [INFO] Filling Email: johndoe@example.com
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:13 [INFO] Selecting Country Code: +91
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:13 [INFO] Clicked Business Unit option: "Home Appliances"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:13 [INFO] Selecting Business Category: Refrigerators
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:14 [INFO] Business Category dropdown is open
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:14 [INFO] Filling Mobile: 9876543210
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:14 [INFO] Typing city: "Aur" — expecting suggestion: "Aurangabad"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:15 [INFO] Clicked Business Category option: "Refrigerators"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:15 [INFO] Clicking Submit button
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:16 [INFO] Submit clicked and response received
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:16 [INFO] Asserting form submission success
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:16 [INFO] First suggestion: "Aurangabad"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:16 [INFO] Selecting Business Unit: Home Appliances
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:17 [INFO] Business Unit dropdown is open
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:18 [INFO] Form submitted successfully. Message: "Thank you for your interest."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:18 [INFO] Clicked Business Unit option: "Home Appliances"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:18 [INFO] Selecting Business Category: Refrigerators
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:18 [INFO] === TC02: City auto-suggestion validation ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:18 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:19 [INFO] Business Category dropdown is open
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:20 [INFO] Clicked Business Category option: "Refrigerators"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:21 [INFO] Filling Message
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:21 [INFO] Attaching file: C:\PlaywrightAutomation\test-data\assets\test-upload.jpg
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:21 [INFO] File attached successfully
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:21 [INFO] Clicking Submit button
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:21 [INFO] Submit clicked and response received
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:21 [INFO] Asserting form submission success
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:24 [INFO] Form submitted successfully. Message: "Thank you for your interest."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:25 [INFO] Suggestions shown: 18
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:25 [INFO] First suggestion: "Aurangabad"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:25 [INFO] === TC03: Business Unit dropdown validation ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:25 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:25 [INFO] City input after selection: "Aurangabad"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:25 [INFO] === TC04: Business Category dropdown validation ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:31 [INFO] Option visible: "Security"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:31 [INFO] Option visible: "Aerospace"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:31 [INFO] Option visible: "Real Estate"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:31 [INFO] Option visible: "Intralogistics"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:31 [INFO] Option visible: "Home Appliances"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:32 [INFO] Option visible: "Locks &amp; Security"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:32 [INFO] Option visible: "Advanced Engineering"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:32 [INFO] Option visible: "Commercial Appliances"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:32 [INFO] Option visible: "Furniture &amp; fittings"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:32 [INFO] Business Unit selected: "Home Appliances"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:32 [INFO] Business Category selected: "Refrigerators"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:32 [INFO] === TC05: File attachment validation ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:32 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:32 [INFO] === TC07: Business Category hidden for Aerospace ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:37 [INFO] Attaching file: C:\PlaywrightAutomation\test-data\assets\test-upload.jpg
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:37 [INFO] File attached successfully
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:38 [INFO] Files attached: 1
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:40 [INFO] === TC06: Required field validation ===
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:40 [INFO] Navigating to enquiry form: https://www.godrejenterprises.com/inquiry
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:40 [INFO] Business Unit selected: "Aerospace"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:40 [INFO] Business Category dropdown is hidden as expected for Aerospace
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:41 [INFO] Test start: #1 Unregistered or wrong credentials: "testuser@example.com"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:41 [INFO] Navigating to https://www.kokuyocamlin.com/camel/login
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:44 [INFO] Entering email: testuser@example.com
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:45 [INFO] Entering password: Password123!
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:45 [INFO] Clicking on login CTA
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:45 [INFO] Assertion passed: Incorrect email or password. Try again. message is visible
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:45 [INFO] Test end: User is not logged in with invalid details
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:46 [INFO] Test start: #2 Invalid email format: "testgmailfd.com"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:46 [INFO] Navigating to https://www.kokuyocamlin.com/camel/login
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:47 [INFO] TC06 passed: Form blocked submission with empty fields
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:47 [INFO] Test start: #5 Unregistered or wrong credentials: "test@gmai"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:47 [INFO] Navigating to https://www.kokuyocamlin.com/camel/login
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:50 [INFO] Entering email: test@gmai
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:51 [INFO] Entering password: password
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:51 [INFO] Entering email: testgmailfd.com
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:51 [INFO] Clicking on login CTA
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:51 [INFO] Entering password: Password1@
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:51 [INFO] Assertion passed: Incorrect email or password. Try again. message is visible
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:51 [INFO] Test end: User is not logged in with invalid details
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:51 [INFO] Assertion passed: Enter a valid email to continue. message is visible
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:52 [INFO] Test start: #3 Invalid password for valid email: "test@test.com"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:52 [INFO] Navigating to https://www.kokuyocamlin.com/camel/login
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:52 [INFO] Test start: #6 Invalid email format: "123"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:55 [INFO] Entering email: test@test.com
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:55 [INFO] Entering email: 123
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:55 [INFO] Entering password: 123
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:55 [INFO] Entering password: Password@
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:55 [INFO] Clicking on login CTA
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:55 [INFO] Assertion passed: Enter a valid email to continue. message is visible
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:55 [INFO] Assertion passed: Incorrect email or password. Try again. message is visible
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:55 [INFO] Test end: User is not logged in with invalid details
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:56 [INFO] Test start: #4 Invalid email format: "@gmail.com"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:56 [INFO] Navigating to https://www.kokuyocamlin.com/camel/login
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:56 [INFO] Test start: #7 Unregistered or wrong credentials: "test.comgmail@"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:58 [INFO] Entering email: test.comgmail@
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:58 [INFO] Entering email: @gmail.com
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:58 [INFO] Entering password: Password1@ '
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:58 [INFO] Clicking on login CTA
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:58 [INFO] Entering password: Password1@
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:58 [INFO] Assertion passed: Incorrect email or password. Try again. message is visible
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:58 [INFO] Test end: User is not logged in with invalid details
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:59 [INFO] Assertion passed: Enter a valid email to continue. message is visible
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:59 [INFO] Test end: User is not logged in with invalid details
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:59 [INFO] Log file for this run: C:\PlaywrightAutomation\logs\2026-04-15.log
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:59 [INFO] Test start: #8 Invalid email format: "OR 1=1 --"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:57:59 [INFO] Navigating to https://www.kokuyocamlin.com/camel/login
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:58:01 [INFO] Entering email: OR 1=1 --
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:58:02 [INFO] Entering password: Password1@
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:58:02 [INFO] Clicking on login CTA
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:58:02 [INFO] Assertion passed: Enter a valid email to continue. message is visible
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:58:02 [INFO] Test end: User is not logged in with invalid details
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 15:58:02 [INFO] Log file for this run: C:\PlaywrightAutomation\logs\2026-04-15.log
 </t>
   </si>
 </sst>
@@ -2341,13 +3060,13 @@
         <v>11</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E7" s="8">
         <v>0</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>1</v>
@@ -2358,19 +3077,19 @@
         <v>30</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" s="8">
         <v>0</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>1</v>
@@ -2381,19 +3100,19 @@
         <v>30</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" s="8">
         <v>0</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>1</v>
@@ -2401,22 +3120,22 @@
     </row>
     <row r="10" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E10" s="8">
         <v>0</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>1</v>
@@ -2424,22 +3143,22 @@
     </row>
     <row r="11" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E11" s="8">
         <v>0</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>1</v>
@@ -2447,7 +3166,7 @@
     </row>
     <row r="12" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>53</v>
@@ -2470,22 +3189,22 @@
     </row>
     <row r="13" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13" s="8">
         <v>0</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>1</v>
@@ -2493,22 +3212,22 @@
     </row>
     <row r="14" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E14" s="8">
         <v>0</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>1</v>
@@ -2516,22 +3235,22 @@
     </row>
     <row r="15" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E15" s="8">
         <v>0</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>1</v>
@@ -2539,22 +3258,22 @@
     </row>
     <row r="16" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E16" s="8">
         <v>0</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>1</v>
@@ -2562,22 +3281,22 @@
     </row>
     <row r="17" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E17" s="8">
         <v>0</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>1</v>
@@ -2585,22 +3304,22 @@
     </row>
     <row r="18" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E18" s="8">
         <v>0</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>1</v>
@@ -2608,22 +3327,22 @@
     </row>
     <row r="19" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E19" s="8">
         <v>0</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>1</v>
@@ -2631,22 +3350,22 @@
     </row>
     <row r="20" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E20" s="8">
         <v>0</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>1</v>
@@ -2654,22 +3373,22 @@
     </row>
     <row r="21" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E21" s="8">
         <v>0</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>1</v>
@@ -2677,22 +3396,22 @@
     </row>
     <row r="22" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E22" s="8">
         <v>0</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>1</v>
@@ -2700,22 +3419,22 @@
     </row>
     <row r="23" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E23" s="8">
         <v>0</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>1</v>
@@ -2723,22 +3442,22 @@
     </row>
     <row r="24" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E24" s="8">
         <v>0</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>1</v>
@@ -2746,22 +3465,22 @@
     </row>
     <row r="25" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E25" s="8">
         <v>0</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>1</v>
@@ -2769,22 +3488,22 @@
     </row>
     <row r="26" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E26" s="8">
         <v>0</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>1</v>
@@ -2792,22 +3511,22 @@
     </row>
     <row r="27" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E27" s="8">
         <v>0</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>1</v>
@@ -2815,22 +3534,22 @@
     </row>
     <row r="28" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E28" s="8">
         <v>0</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>1</v>
@@ -2838,22 +3557,22 @@
     </row>
     <row r="29" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E29" s="8">
         <v>0</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>1</v>
@@ -2861,22 +3580,22 @@
     </row>
     <row r="30" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E30" s="8">
         <v>0</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G30" s="10" t="s">
         <v>1</v>
@@ -2904,22 +3623,22 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>14</v>
@@ -2927,22 +3646,22 @@
     </row>
     <row r="2" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G2" s="14" t="s">
         <v>11</v>
@@ -2950,7 +3669,7 @@
     </row>
     <row r="3" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>23</v>
@@ -2959,13 +3678,13 @@
         <v>24</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>11</v>
@@ -2973,22 +3692,22 @@
     </row>
     <row r="4" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G4" s="14" t="s">
         <v>11</v>
@@ -2996,22 +3715,22 @@
     </row>
     <row r="5" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>30</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>11</v>
@@ -3019,22 +3738,22 @@
     </row>
     <row r="6" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>30</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G6" s="14" t="s">
         <v>11</v>
@@ -3042,22 +3761,22 @@
     </row>
     <row r="7" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>11</v>
@@ -3065,22 +3784,22 @@
     </row>
     <row r="8" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G8" s="14" t="s">
         <v>11</v>
@@ -3088,22 +3807,22 @@
     </row>
     <row r="9" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>11</v>
@@ -3111,22 +3830,22 @@
     </row>
     <row r="10" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G10" s="14" t="s">
         <v>11</v>
@@ -3134,22 +3853,22 @@
     </row>
     <row r="11" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>11</v>
@@ -3157,22 +3876,22 @@
     </row>
     <row r="12" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G12" s="14" t="s">
         <v>11</v>
@@ -3180,22 +3899,22 @@
     </row>
     <row r="13" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>11</v>
@@ -3203,22 +3922,22 @@
     </row>
     <row r="14" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G14" s="14" t="s">
         <v>11</v>
@@ -3226,22 +3945,22 @@
     </row>
     <row r="15" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G15" s="14" t="s">
         <v>11</v>
@@ -3249,22 +3968,22 @@
     </row>
     <row r="16" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="E16" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>178</v>
-      </c>
       <c r="F16" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G16" s="14" t="s">
         <v>11</v>
@@ -3272,22 +3991,22 @@
     </row>
     <row r="17" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="F17" s="16" t="s">
         <v>131</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>130</v>
       </c>
       <c r="G17" s="14" t="s">
         <v>11</v>
@@ -3295,22 +4014,22 @@
     </row>
     <row r="18" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G18" s="14" t="s">
         <v>11</v>
@@ -3318,22 +4037,22 @@
     </row>
     <row r="19" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G19" s="14" t="s">
         <v>11</v>
@@ -3341,22 +4060,22 @@
     </row>
     <row r="20" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G20" s="14" t="s">
         <v>11</v>
@@ -3364,22 +4083,22 @@
     </row>
     <row r="21" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G21" s="14" t="s">
         <v>11</v>
@@ -3387,22 +4106,22 @@
     </row>
     <row r="22" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>198</v>
+        <v>93</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>199</v>
+        <v>133</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G22" s="14" t="s">
         <v>11</v>
@@ -3410,22 +4129,22 @@
     </row>
     <row r="23" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="B23" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>132</v>
-      </c>
       <c r="E23" s="15" t="s">
-        <v>132</v>
+        <v>202</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G23" s="14" t="s">
         <v>11</v>
@@ -3433,22 +4152,22 @@
     </row>
     <row r="24" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G24" s="14" t="s">
         <v>11</v>
@@ -3456,22 +4175,22 @@
     </row>
     <row r="25" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G25" s="14" t="s">
         <v>11</v>
@@ -3479,22 +4198,22 @@
     </row>
     <row r="26" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G26" s="14" t="s">
         <v>11</v>
@@ -3502,22 +4221,22 @@
     </row>
     <row r="27" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G27" s="14" t="s">
         <v>11</v>
@@ -3525,22 +4244,22 @@
     </row>
     <row r="28" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G28" s="14" t="s">
         <v>11</v>
@@ -3548,22 +4267,22 @@
     </row>
     <row r="29" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>11</v>
@@ -3571,22 +4290,22 @@
     </row>
     <row r="30" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G30" s="14" t="s">
         <v>11</v>
@@ -3601,7 +4320,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C189"/>
+  <dimension ref="A1:C377"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -3611,13 +4330,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -3628,7 +4347,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -3639,7 +4358,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -3650,7 +4369,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -3661,7 +4380,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -3672,7 +4391,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -3683,7 +4402,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -3694,7 +4413,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -3705,7 +4424,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -3716,7 +4435,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -3727,7 +4446,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -3738,7 +4457,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -3749,7 +4468,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -3760,7 +4479,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -3771,7 +4490,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -3782,7 +4501,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -3793,7 +4512,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -3804,7 +4523,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -3815,7 +4534,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -3826,7 +4545,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -3837,7 +4556,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -3848,7 +4567,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -3859,7 +4578,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -3870,7 +4589,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -3881,7 +4600,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -3892,7 +4611,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -3903,7 +4622,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -3914,7 +4633,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -3925,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -3936,7 +4655,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -3947,7 +4666,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -3958,7 +4677,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -3969,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -3980,7 +4699,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -3991,7 +4710,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -4002,7 +4721,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -4013,7 +4732,7 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -4024,7 +4743,7 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -4035,7 +4754,7 @@
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -4046,7 +4765,7 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -4057,7 +4776,7 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -4068,7 +4787,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -4079,7 +4798,7 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -4090,7 +4809,7 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -4101,7 +4820,7 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -4112,7 +4831,7 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -4123,7 +4842,7 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -4134,7 +4853,7 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -4145,7 +4864,7 @@
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -4156,7 +4875,7 @@
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -4167,7 +4886,7 @@
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -4178,7 +4897,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -4189,7 +4908,7 @@
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -4200,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -4211,7 +4930,7 @@
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -4222,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -4233,7 +4952,7 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -4244,7 +4963,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -4255,7 +4974,7 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -4266,7 +4985,7 @@
         <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -4277,7 +4996,7 @@
         <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -4288,7 +5007,7 @@
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -4299,7 +5018,7 @@
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -4310,7 +5029,7 @@
         <v>1</v>
       </c>
       <c r="C64" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -4321,7 +5040,7 @@
         <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -4332,7 +5051,7 @@
         <v>1</v>
       </c>
       <c r="C66" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -4343,7 +5062,7 @@
         <v>1</v>
       </c>
       <c r="C67" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -4354,7 +5073,7 @@
         <v>1</v>
       </c>
       <c r="C68" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -4365,7 +5084,7 @@
         <v>1</v>
       </c>
       <c r="C69" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -4376,7 +5095,7 @@
         <v>1</v>
       </c>
       <c r="C70" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -4387,7 +5106,7 @@
         <v>1</v>
       </c>
       <c r="C71" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -4398,7 +5117,7 @@
         <v>1</v>
       </c>
       <c r="C72" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -4409,7 +5128,7 @@
         <v>1</v>
       </c>
       <c r="C73" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -4420,7 +5139,7 @@
         <v>1</v>
       </c>
       <c r="C74" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -4431,7 +5150,7 @@
         <v>1</v>
       </c>
       <c r="C75" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -4442,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="C76" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -4453,7 +5172,7 @@
         <v>1</v>
       </c>
       <c r="C77" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -4464,7 +5183,7 @@
         <v>1</v>
       </c>
       <c r="C78" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -4475,7 +5194,7 @@
         <v>1</v>
       </c>
       <c r="C79" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -4486,7 +5205,7 @@
         <v>1</v>
       </c>
       <c r="C80" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -4497,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="C81" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -4508,7 +5227,7 @@
         <v>1</v>
       </c>
       <c r="C82" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -4519,7 +5238,7 @@
         <v>1</v>
       </c>
       <c r="C83" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -4530,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="C84" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -4541,7 +5260,7 @@
         <v>1</v>
       </c>
       <c r="C85" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -4552,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="C86" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -4563,7 +5282,7 @@
         <v>1</v>
       </c>
       <c r="C87" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -4574,7 +5293,7 @@
         <v>1</v>
       </c>
       <c r="C88" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -4585,7 +5304,7 @@
         <v>1</v>
       </c>
       <c r="C89" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -4596,7 +5315,7 @@
         <v>1</v>
       </c>
       <c r="C90" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -4607,7 +5326,7 @@
         <v>1</v>
       </c>
       <c r="C91" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -4618,7 +5337,7 @@
         <v>1</v>
       </c>
       <c r="C92" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -4629,7 +5348,7 @@
         <v>1</v>
       </c>
       <c r="C93" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -4640,7 +5359,7 @@
         <v>1</v>
       </c>
       <c r="C94" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -4651,7 +5370,7 @@
         <v>1</v>
       </c>
       <c r="C95" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -4662,7 +5381,7 @@
         <v>1</v>
       </c>
       <c r="C96" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -4673,7 +5392,7 @@
         <v>1</v>
       </c>
       <c r="C97" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -4684,7 +5403,7 @@
         <v>1</v>
       </c>
       <c r="C98" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -4695,7 +5414,7 @@
         <v>1</v>
       </c>
       <c r="C99" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -4706,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="C100" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -4717,7 +5436,7 @@
         <v>1</v>
       </c>
       <c r="C101" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -4728,7 +5447,7 @@
         <v>1</v>
       </c>
       <c r="C102" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -4739,7 +5458,7 @@
         <v>1</v>
       </c>
       <c r="C103" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -4750,7 +5469,7 @@
         <v>1</v>
       </c>
       <c r="C104" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -4761,7 +5480,7 @@
         <v>1</v>
       </c>
       <c r="C105" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -4772,7 +5491,7 @@
         <v>1</v>
       </c>
       <c r="C106" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -4783,7 +5502,7 @@
         <v>1</v>
       </c>
       <c r="C107" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -4794,7 +5513,7 @@
         <v>1</v>
       </c>
       <c r="C108" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -4805,7 +5524,7 @@
         <v>1</v>
       </c>
       <c r="C109" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -4816,7 +5535,7 @@
         <v>1</v>
       </c>
       <c r="C110" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -4827,7 +5546,7 @@
         <v>1</v>
       </c>
       <c r="C111" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -4838,7 +5557,7 @@
         <v>1</v>
       </c>
       <c r="C112" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -4849,7 +5568,7 @@
         <v>1</v>
       </c>
       <c r="C113" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -4860,7 +5579,7 @@
         <v>1</v>
       </c>
       <c r="C114" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -4871,7 +5590,7 @@
         <v>1</v>
       </c>
       <c r="C115" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -4882,7 +5601,7 @@
         <v>1</v>
       </c>
       <c r="C116" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -4893,7 +5612,7 @@
         <v>1</v>
       </c>
       <c r="C117" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -4904,7 +5623,7 @@
         <v>1</v>
       </c>
       <c r="C118" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -4915,7 +5634,7 @@
         <v>1</v>
       </c>
       <c r="C119" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -4926,7 +5645,7 @@
         <v>1</v>
       </c>
       <c r="C120" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -4937,7 +5656,7 @@
         <v>1</v>
       </c>
       <c r="C121" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -4948,7 +5667,7 @@
         <v>1</v>
       </c>
       <c r="C122" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -4959,7 +5678,7 @@
         <v>1</v>
       </c>
       <c r="C123" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -4970,7 +5689,7 @@
         <v>1</v>
       </c>
       <c r="C124" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -4981,7 +5700,7 @@
         <v>1</v>
       </c>
       <c r="C125" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -4992,7 +5711,7 @@
         <v>1</v>
       </c>
       <c r="C126" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -5003,7 +5722,7 @@
         <v>1</v>
       </c>
       <c r="C127" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -5014,7 +5733,7 @@
         <v>1</v>
       </c>
       <c r="C128" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -5025,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="C129" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -5036,7 +5755,7 @@
         <v>1</v>
       </c>
       <c r="C130" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -5047,7 +5766,7 @@
         <v>1</v>
       </c>
       <c r="C131" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -5058,7 +5777,7 @@
         <v>1</v>
       </c>
       <c r="C132" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -5069,7 +5788,7 @@
         <v>1</v>
       </c>
       <c r="C133" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -5080,7 +5799,7 @@
         <v>1</v>
       </c>
       <c r="C134" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -5091,7 +5810,7 @@
         <v>1</v>
       </c>
       <c r="C135" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -5102,7 +5821,7 @@
         <v>1</v>
       </c>
       <c r="C136" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -5113,7 +5832,7 @@
         <v>1</v>
       </c>
       <c r="C137" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -5124,7 +5843,7 @@
         <v>1</v>
       </c>
       <c r="C138" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -5135,7 +5854,7 @@
         <v>1</v>
       </c>
       <c r="C139" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -5146,7 +5865,7 @@
         <v>1</v>
       </c>
       <c r="C140" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -5157,7 +5876,7 @@
         <v>1</v>
       </c>
       <c r="C141" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -5168,7 +5887,7 @@
         <v>1</v>
       </c>
       <c r="C142" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -5179,7 +5898,7 @@
         <v>1</v>
       </c>
       <c r="C143" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -5190,7 +5909,7 @@
         <v>1</v>
       </c>
       <c r="C144" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -5201,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="C145" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -5212,7 +5931,7 @@
         <v>1</v>
       </c>
       <c r="C146" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -5223,7 +5942,7 @@
         <v>1</v>
       </c>
       <c r="C147" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -5234,7 +5953,7 @@
         <v>1</v>
       </c>
       <c r="C148" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -5245,7 +5964,7 @@
         <v>1</v>
       </c>
       <c r="C149" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -5256,7 +5975,7 @@
         <v>1</v>
       </c>
       <c r="C150" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -5267,7 +5986,7 @@
         <v>1</v>
       </c>
       <c r="C151" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -5278,7 +5997,7 @@
         <v>1</v>
       </c>
       <c r="C152" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -5289,7 +6008,7 @@
         <v>1</v>
       </c>
       <c r="C153" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -5300,7 +6019,7 @@
         <v>1</v>
       </c>
       <c r="C154" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -5311,7 +6030,7 @@
         <v>1</v>
       </c>
       <c r="C155" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -5322,7 +6041,7 @@
         <v>1</v>
       </c>
       <c r="C156" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -5333,7 +6052,7 @@
         <v>1</v>
       </c>
       <c r="C157" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -5344,7 +6063,7 @@
         <v>1</v>
       </c>
       <c r="C158" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -5355,7 +6074,7 @@
         <v>1</v>
       </c>
       <c r="C159" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -5366,7 +6085,7 @@
         <v>1</v>
       </c>
       <c r="C160" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -5377,7 +6096,7 @@
         <v>1</v>
       </c>
       <c r="C161" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -5388,7 +6107,7 @@
         <v>1</v>
       </c>
       <c r="C162" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -5399,7 +6118,7 @@
         <v>1</v>
       </c>
       <c r="C163" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -5410,7 +6129,7 @@
         <v>1</v>
       </c>
       <c r="C164" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -5421,7 +6140,7 @@
         <v>1</v>
       </c>
       <c r="C165" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -5432,7 +6151,7 @@
         <v>1</v>
       </c>
       <c r="C166" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -5443,7 +6162,7 @@
         <v>1</v>
       </c>
       <c r="C167" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -5454,7 +6173,7 @@
         <v>1</v>
       </c>
       <c r="C168" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -5465,7 +6184,7 @@
         <v>1</v>
       </c>
       <c r="C169" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -5476,7 +6195,7 @@
         <v>1</v>
       </c>
       <c r="C170" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -5487,7 +6206,7 @@
         <v>1</v>
       </c>
       <c r="C171" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -5498,7 +6217,7 @@
         <v>1</v>
       </c>
       <c r="C172" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -5509,7 +6228,7 @@
         <v>1</v>
       </c>
       <c r="C173" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -5520,7 +6239,7 @@
         <v>1</v>
       </c>
       <c r="C174" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -5531,7 +6250,7 @@
         <v>1</v>
       </c>
       <c r="C175" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -5542,7 +6261,7 @@
         <v>1</v>
       </c>
       <c r="C176" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -5553,7 +6272,7 @@
         <v>1</v>
       </c>
       <c r="C177" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -5564,7 +6283,7 @@
         <v>1</v>
       </c>
       <c r="C178" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -5575,7 +6294,7 @@
         <v>1</v>
       </c>
       <c r="C179" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -5586,7 +6305,7 @@
         <v>1</v>
       </c>
       <c r="C180" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -5597,7 +6316,7 @@
         <v>1</v>
       </c>
       <c r="C181" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -5608,7 +6327,7 @@
         <v>1</v>
       </c>
       <c r="C182" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -5619,7 +6338,7 @@
         <v>1</v>
       </c>
       <c r="C183" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -5630,7 +6349,7 @@
         <v>1</v>
       </c>
       <c r="C184" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -5641,7 +6360,7 @@
         <v>1</v>
       </c>
       <c r="C185" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -5652,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="C186" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -5663,7 +6382,7 @@
         <v>1</v>
       </c>
       <c r="C187" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -5674,7 +6393,7 @@
         <v>1</v>
       </c>
       <c r="C188" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -5685,7 +6404,2075 @@
         <v>1</v>
       </c>
       <c r="C189" t="s">
-        <v>387</v>
+        <v>388</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>1</v>
+      </c>
+      <c r="B190" t="s">
+        <v>1</v>
+      </c>
+      <c r="C190" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>1</v>
+      </c>
+      <c r="B191" t="s">
+        <v>1</v>
+      </c>
+      <c r="C191" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>1</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1</v>
+      </c>
+      <c r="C192" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>1</v>
+      </c>
+      <c r="B193" t="s">
+        <v>1</v>
+      </c>
+      <c r="C193" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>1</v>
+      </c>
+      <c r="B194" t="s">
+        <v>1</v>
+      </c>
+      <c r="C194" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>1</v>
+      </c>
+      <c r="B195" t="s">
+        <v>1</v>
+      </c>
+      <c r="C195" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>1</v>
+      </c>
+      <c r="B196" t="s">
+        <v>1</v>
+      </c>
+      <c r="C196" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>1</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1</v>
+      </c>
+      <c r="C197" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>1</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1</v>
+      </c>
+      <c r="C198" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>1</v>
+      </c>
+      <c r="B199" t="s">
+        <v>1</v>
+      </c>
+      <c r="C199" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>1</v>
+      </c>
+      <c r="B200" t="s">
+        <v>1</v>
+      </c>
+      <c r="C200" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>1</v>
+      </c>
+      <c r="B201" t="s">
+        <v>1</v>
+      </c>
+      <c r="C201" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>1</v>
+      </c>
+      <c r="B202" t="s">
+        <v>1</v>
+      </c>
+      <c r="C202" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>1</v>
+      </c>
+      <c r="B203" t="s">
+        <v>1</v>
+      </c>
+      <c r="C203" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>1</v>
+      </c>
+      <c r="B204" t="s">
+        <v>1</v>
+      </c>
+      <c r="C204" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>1</v>
+      </c>
+      <c r="B205" t="s">
+        <v>1</v>
+      </c>
+      <c r="C205" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>1</v>
+      </c>
+      <c r="B206" t="s">
+        <v>1</v>
+      </c>
+      <c r="C206" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>1</v>
+      </c>
+      <c r="B207" t="s">
+        <v>1</v>
+      </c>
+      <c r="C207" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>1</v>
+      </c>
+      <c r="B208" t="s">
+        <v>1</v>
+      </c>
+      <c r="C208" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>1</v>
+      </c>
+      <c r="B209" t="s">
+        <v>1</v>
+      </c>
+      <c r="C209" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>1</v>
+      </c>
+      <c r="B210" t="s">
+        <v>1</v>
+      </c>
+      <c r="C210" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>1</v>
+      </c>
+      <c r="B211" t="s">
+        <v>1</v>
+      </c>
+      <c r="C211" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>1</v>
+      </c>
+      <c r="B212" t="s">
+        <v>1</v>
+      </c>
+      <c r="C212" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>1</v>
+      </c>
+      <c r="B213" t="s">
+        <v>1</v>
+      </c>
+      <c r="C213" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>1</v>
+      </c>
+      <c r="B214" t="s">
+        <v>1</v>
+      </c>
+      <c r="C214" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>1</v>
+      </c>
+      <c r="B215" t="s">
+        <v>1</v>
+      </c>
+      <c r="C215" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>1</v>
+      </c>
+      <c r="B216" t="s">
+        <v>1</v>
+      </c>
+      <c r="C216" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>1</v>
+      </c>
+      <c r="B217" t="s">
+        <v>1</v>
+      </c>
+      <c r="C217" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>1</v>
+      </c>
+      <c r="B218" t="s">
+        <v>1</v>
+      </c>
+      <c r="C218" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>1</v>
+      </c>
+      <c r="B219" t="s">
+        <v>1</v>
+      </c>
+      <c r="C219" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>1</v>
+      </c>
+      <c r="B220" t="s">
+        <v>1</v>
+      </c>
+      <c r="C220" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>1</v>
+      </c>
+      <c r="B221" t="s">
+        <v>1</v>
+      </c>
+      <c r="C221" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>1</v>
+      </c>
+      <c r="B222" t="s">
+        <v>1</v>
+      </c>
+      <c r="C222" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>1</v>
+      </c>
+      <c r="B223" t="s">
+        <v>1</v>
+      </c>
+      <c r="C223" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>1</v>
+      </c>
+      <c r="B224" t="s">
+        <v>1</v>
+      </c>
+      <c r="C224" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>1</v>
+      </c>
+      <c r="B225" t="s">
+        <v>1</v>
+      </c>
+      <c r="C225" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>1</v>
+      </c>
+      <c r="B226" t="s">
+        <v>1</v>
+      </c>
+      <c r="C226" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>1</v>
+      </c>
+      <c r="B227" t="s">
+        <v>1</v>
+      </c>
+      <c r="C227" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>1</v>
+      </c>
+      <c r="B228" t="s">
+        <v>1</v>
+      </c>
+      <c r="C228" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>1</v>
+      </c>
+      <c r="B229" t="s">
+        <v>1</v>
+      </c>
+      <c r="C229" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>1</v>
+      </c>
+      <c r="B230" t="s">
+        <v>1</v>
+      </c>
+      <c r="C230" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>1</v>
+      </c>
+      <c r="B231" t="s">
+        <v>1</v>
+      </c>
+      <c r="C231" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>1</v>
+      </c>
+      <c r="B232" t="s">
+        <v>1</v>
+      </c>
+      <c r="C232" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>1</v>
+      </c>
+      <c r="B233" t="s">
+        <v>1</v>
+      </c>
+      <c r="C233" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>1</v>
+      </c>
+      <c r="B234" t="s">
+        <v>1</v>
+      </c>
+      <c r="C234" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>1</v>
+      </c>
+      <c r="B235" t="s">
+        <v>1</v>
+      </c>
+      <c r="C235" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>1</v>
+      </c>
+      <c r="B236" t="s">
+        <v>1</v>
+      </c>
+      <c r="C236" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>1</v>
+      </c>
+      <c r="B237" t="s">
+        <v>1</v>
+      </c>
+      <c r="C237" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>1</v>
+      </c>
+      <c r="B238" t="s">
+        <v>1</v>
+      </c>
+      <c r="C238" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>1</v>
+      </c>
+      <c r="B239" t="s">
+        <v>1</v>
+      </c>
+      <c r="C239" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>1</v>
+      </c>
+      <c r="B240" t="s">
+        <v>1</v>
+      </c>
+      <c r="C240" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>1</v>
+      </c>
+      <c r="B241" t="s">
+        <v>1</v>
+      </c>
+      <c r="C241" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>1</v>
+      </c>
+      <c r="B242" t="s">
+        <v>1</v>
+      </c>
+      <c r="C242" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>1</v>
+      </c>
+      <c r="B243" t="s">
+        <v>1</v>
+      </c>
+      <c r="C243" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>1</v>
+      </c>
+      <c r="B244" t="s">
+        <v>1</v>
+      </c>
+      <c r="C244" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>1</v>
+      </c>
+      <c r="B245" t="s">
+        <v>1</v>
+      </c>
+      <c r="C245" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>1</v>
+      </c>
+      <c r="B246" t="s">
+        <v>1</v>
+      </c>
+      <c r="C246" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>1</v>
+      </c>
+      <c r="B247" t="s">
+        <v>1</v>
+      </c>
+      <c r="C247" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>1</v>
+      </c>
+      <c r="B248" t="s">
+        <v>1</v>
+      </c>
+      <c r="C248" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>1</v>
+      </c>
+      <c r="B249" t="s">
+        <v>1</v>
+      </c>
+      <c r="C249" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>1</v>
+      </c>
+      <c r="B250" t="s">
+        <v>1</v>
+      </c>
+      <c r="C250" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>1</v>
+      </c>
+      <c r="B251" t="s">
+        <v>1</v>
+      </c>
+      <c r="C251" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>1</v>
+      </c>
+      <c r="B252" t="s">
+        <v>1</v>
+      </c>
+      <c r="C252" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>1</v>
+      </c>
+      <c r="B253" t="s">
+        <v>1</v>
+      </c>
+      <c r="C253" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>1</v>
+      </c>
+      <c r="B254" t="s">
+        <v>1</v>
+      </c>
+      <c r="C254" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>1</v>
+      </c>
+      <c r="B255" t="s">
+        <v>1</v>
+      </c>
+      <c r="C255" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>1</v>
+      </c>
+      <c r="B256" t="s">
+        <v>1</v>
+      </c>
+      <c r="C256" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>1</v>
+      </c>
+      <c r="B257" t="s">
+        <v>1</v>
+      </c>
+      <c r="C257" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>1</v>
+      </c>
+      <c r="B258" t="s">
+        <v>1</v>
+      </c>
+      <c r="C258" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>1</v>
+      </c>
+      <c r="B259" t="s">
+        <v>1</v>
+      </c>
+      <c r="C259" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>1</v>
+      </c>
+      <c r="B260" t="s">
+        <v>1</v>
+      </c>
+      <c r="C260" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>1</v>
+      </c>
+      <c r="B261" t="s">
+        <v>1</v>
+      </c>
+      <c r="C261" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>1</v>
+      </c>
+      <c r="B262" t="s">
+        <v>1</v>
+      </c>
+      <c r="C262" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>1</v>
+      </c>
+      <c r="B263" t="s">
+        <v>1</v>
+      </c>
+      <c r="C263" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>1</v>
+      </c>
+      <c r="B264" t="s">
+        <v>1</v>
+      </c>
+      <c r="C264" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>1</v>
+      </c>
+      <c r="B265" t="s">
+        <v>1</v>
+      </c>
+      <c r="C265" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>1</v>
+      </c>
+      <c r="B266" t="s">
+        <v>1</v>
+      </c>
+      <c r="C266" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>1</v>
+      </c>
+      <c r="B267" t="s">
+        <v>1</v>
+      </c>
+      <c r="C267" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>1</v>
+      </c>
+      <c r="B268" t="s">
+        <v>1</v>
+      </c>
+      <c r="C268" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>1</v>
+      </c>
+      <c r="B269" t="s">
+        <v>1</v>
+      </c>
+      <c r="C269" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>1</v>
+      </c>
+      <c r="B270" t="s">
+        <v>1</v>
+      </c>
+      <c r="C270" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>1</v>
+      </c>
+      <c r="B271" t="s">
+        <v>1</v>
+      </c>
+      <c r="C271" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>1</v>
+      </c>
+      <c r="B272" t="s">
+        <v>1</v>
+      </c>
+      <c r="C272" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>1</v>
+      </c>
+      <c r="B273" t="s">
+        <v>1</v>
+      </c>
+      <c r="C273" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>1</v>
+      </c>
+      <c r="B274" t="s">
+        <v>1</v>
+      </c>
+      <c r="C274" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>1</v>
+      </c>
+      <c r="B275" t="s">
+        <v>1</v>
+      </c>
+      <c r="C275" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>1</v>
+      </c>
+      <c r="B276" t="s">
+        <v>1</v>
+      </c>
+      <c r="C276" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>1</v>
+      </c>
+      <c r="B277" t="s">
+        <v>1</v>
+      </c>
+      <c r="C277" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>1</v>
+      </c>
+      <c r="B278" t="s">
+        <v>1</v>
+      </c>
+      <c r="C278" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>1</v>
+      </c>
+      <c r="B279" t="s">
+        <v>1</v>
+      </c>
+      <c r="C279" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>1</v>
+      </c>
+      <c r="B280" t="s">
+        <v>1</v>
+      </c>
+      <c r="C280" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>1</v>
+      </c>
+      <c r="B281" t="s">
+        <v>1</v>
+      </c>
+      <c r="C281" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>1</v>
+      </c>
+      <c r="B282" t="s">
+        <v>1</v>
+      </c>
+      <c r="C282" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>1</v>
+      </c>
+      <c r="B283" t="s">
+        <v>1</v>
+      </c>
+      <c r="C283" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>1</v>
+      </c>
+      <c r="B284" t="s">
+        <v>1</v>
+      </c>
+      <c r="C284" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>1</v>
+      </c>
+      <c r="B285" t="s">
+        <v>1</v>
+      </c>
+      <c r="C285" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>1</v>
+      </c>
+      <c r="B286" t="s">
+        <v>1</v>
+      </c>
+      <c r="C286" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>1</v>
+      </c>
+      <c r="B287" t="s">
+        <v>1</v>
+      </c>
+      <c r="C287" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>1</v>
+      </c>
+      <c r="B288" t="s">
+        <v>1</v>
+      </c>
+      <c r="C288" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>1</v>
+      </c>
+      <c r="B289" t="s">
+        <v>1</v>
+      </c>
+      <c r="C289" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>1</v>
+      </c>
+      <c r="B290" t="s">
+        <v>1</v>
+      </c>
+      <c r="C290" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>1</v>
+      </c>
+      <c r="B291" t="s">
+        <v>1</v>
+      </c>
+      <c r="C291" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>1</v>
+      </c>
+      <c r="B292" t="s">
+        <v>1</v>
+      </c>
+      <c r="C292" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>1</v>
+      </c>
+      <c r="B293" t="s">
+        <v>1</v>
+      </c>
+      <c r="C293" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>1</v>
+      </c>
+      <c r="B294" t="s">
+        <v>1</v>
+      </c>
+      <c r="C294" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>1</v>
+      </c>
+      <c r="B295" t="s">
+        <v>1</v>
+      </c>
+      <c r="C295" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>1</v>
+      </c>
+      <c r="B296" t="s">
+        <v>1</v>
+      </c>
+      <c r="C296" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>1</v>
+      </c>
+      <c r="B297" t="s">
+        <v>1</v>
+      </c>
+      <c r="C297" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>1</v>
+      </c>
+      <c r="B298" t="s">
+        <v>1</v>
+      </c>
+      <c r="C298" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>1</v>
+      </c>
+      <c r="B299" t="s">
+        <v>1</v>
+      </c>
+      <c r="C299" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>1</v>
+      </c>
+      <c r="B300" t="s">
+        <v>1</v>
+      </c>
+      <c r="C300" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>1</v>
+      </c>
+      <c r="B301" t="s">
+        <v>1</v>
+      </c>
+      <c r="C301" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>1</v>
+      </c>
+      <c r="B302" t="s">
+        <v>1</v>
+      </c>
+      <c r="C302" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>1</v>
+      </c>
+      <c r="B303" t="s">
+        <v>1</v>
+      </c>
+      <c r="C303" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>1</v>
+      </c>
+      <c r="B304" t="s">
+        <v>1</v>
+      </c>
+      <c r="C304" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>1</v>
+      </c>
+      <c r="B305" t="s">
+        <v>1</v>
+      </c>
+      <c r="C305" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>1</v>
+      </c>
+      <c r="B306" t="s">
+        <v>1</v>
+      </c>
+      <c r="C306" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>1</v>
+      </c>
+      <c r="B307" t="s">
+        <v>1</v>
+      </c>
+      <c r="C307" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>1</v>
+      </c>
+      <c r="B308" t="s">
+        <v>1</v>
+      </c>
+      <c r="C308" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>1</v>
+      </c>
+      <c r="B309" t="s">
+        <v>1</v>
+      </c>
+      <c r="C309" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>1</v>
+      </c>
+      <c r="B310" t="s">
+        <v>1</v>
+      </c>
+      <c r="C310" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>1</v>
+      </c>
+      <c r="B311" t="s">
+        <v>1</v>
+      </c>
+      <c r="C311" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>1</v>
+      </c>
+      <c r="B312" t="s">
+        <v>1</v>
+      </c>
+      <c r="C312" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>1</v>
+      </c>
+      <c r="B313" t="s">
+        <v>1</v>
+      </c>
+      <c r="C313" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>1</v>
+      </c>
+      <c r="B314" t="s">
+        <v>1</v>
+      </c>
+      <c r="C314" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>1</v>
+      </c>
+      <c r="B315" t="s">
+        <v>1</v>
+      </c>
+      <c r="C315" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>1</v>
+      </c>
+      <c r="B316" t="s">
+        <v>1</v>
+      </c>
+      <c r="C316" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>1</v>
+      </c>
+      <c r="B317" t="s">
+        <v>1</v>
+      </c>
+      <c r="C317" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>1</v>
+      </c>
+      <c r="B318" t="s">
+        <v>1</v>
+      </c>
+      <c r="C318" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>1</v>
+      </c>
+      <c r="B319" t="s">
+        <v>1</v>
+      </c>
+      <c r="C319" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>1</v>
+      </c>
+      <c r="B320" t="s">
+        <v>1</v>
+      </c>
+      <c r="C320" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>1</v>
+      </c>
+      <c r="B321" t="s">
+        <v>1</v>
+      </c>
+      <c r="C321" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>1</v>
+      </c>
+      <c r="B322" t="s">
+        <v>1</v>
+      </c>
+      <c r="C322" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>1</v>
+      </c>
+      <c r="B323" t="s">
+        <v>1</v>
+      </c>
+      <c r="C323" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>1</v>
+      </c>
+      <c r="B324" t="s">
+        <v>1</v>
+      </c>
+      <c r="C324" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>1</v>
+      </c>
+      <c r="B325" t="s">
+        <v>1</v>
+      </c>
+      <c r="C325" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>1</v>
+      </c>
+      <c r="B326" t="s">
+        <v>1</v>
+      </c>
+      <c r="C326" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>1</v>
+      </c>
+      <c r="B327" t="s">
+        <v>1</v>
+      </c>
+      <c r="C327" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>1</v>
+      </c>
+      <c r="B328" t="s">
+        <v>1</v>
+      </c>
+      <c r="C328" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>1</v>
+      </c>
+      <c r="B329" t="s">
+        <v>1</v>
+      </c>
+      <c r="C329" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>1</v>
+      </c>
+      <c r="B330" t="s">
+        <v>1</v>
+      </c>
+      <c r="C330" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>1</v>
+      </c>
+      <c r="B331" t="s">
+        <v>1</v>
+      </c>
+      <c r="C331" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>1</v>
+      </c>
+      <c r="B332" t="s">
+        <v>1</v>
+      </c>
+      <c r="C332" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>1</v>
+      </c>
+      <c r="B333" t="s">
+        <v>1</v>
+      </c>
+      <c r="C333" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>1</v>
+      </c>
+      <c r="B334" t="s">
+        <v>1</v>
+      </c>
+      <c r="C334" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>1</v>
+      </c>
+      <c r="B335" t="s">
+        <v>1</v>
+      </c>
+      <c r="C335" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>1</v>
+      </c>
+      <c r="B336" t="s">
+        <v>1</v>
+      </c>
+      <c r="C336" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>1</v>
+      </c>
+      <c r="B337" t="s">
+        <v>1</v>
+      </c>
+      <c r="C337" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>1</v>
+      </c>
+      <c r="B338" t="s">
+        <v>1</v>
+      </c>
+      <c r="C338" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>1</v>
+      </c>
+      <c r="B339" t="s">
+        <v>1</v>
+      </c>
+      <c r="C339" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>1</v>
+      </c>
+      <c r="B340" t="s">
+        <v>1</v>
+      </c>
+      <c r="C340" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>1</v>
+      </c>
+      <c r="B341" t="s">
+        <v>1</v>
+      </c>
+      <c r="C341" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>1</v>
+      </c>
+      <c r="B342" t="s">
+        <v>1</v>
+      </c>
+      <c r="C342" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>1</v>
+      </c>
+      <c r="B343" t="s">
+        <v>1</v>
+      </c>
+      <c r="C343" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>1</v>
+      </c>
+      <c r="B344" t="s">
+        <v>1</v>
+      </c>
+      <c r="C344" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>1</v>
+      </c>
+      <c r="B345" t="s">
+        <v>1</v>
+      </c>
+      <c r="C345" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>1</v>
+      </c>
+      <c r="B346" t="s">
+        <v>1</v>
+      </c>
+      <c r="C346" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>1</v>
+      </c>
+      <c r="B347" t="s">
+        <v>1</v>
+      </c>
+      <c r="C347" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>1</v>
+      </c>
+      <c r="B348" t="s">
+        <v>1</v>
+      </c>
+      <c r="C348" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>1</v>
+      </c>
+      <c r="B349" t="s">
+        <v>1</v>
+      </c>
+      <c r="C349" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>1</v>
+      </c>
+      <c r="B350" t="s">
+        <v>1</v>
+      </c>
+      <c r="C350" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>1</v>
+      </c>
+      <c r="B351" t="s">
+        <v>1</v>
+      </c>
+      <c r="C351" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>1</v>
+      </c>
+      <c r="B352" t="s">
+        <v>1</v>
+      </c>
+      <c r="C352" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>1</v>
+      </c>
+      <c r="B353" t="s">
+        <v>1</v>
+      </c>
+      <c r="C353" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>1</v>
+      </c>
+      <c r="B354" t="s">
+        <v>1</v>
+      </c>
+      <c r="C354" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>1</v>
+      </c>
+      <c r="B355" t="s">
+        <v>1</v>
+      </c>
+      <c r="C355" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>1</v>
+      </c>
+      <c r="B356" t="s">
+        <v>1</v>
+      </c>
+      <c r="C356" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>1</v>
+      </c>
+      <c r="B357" t="s">
+        <v>1</v>
+      </c>
+      <c r="C357" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>1</v>
+      </c>
+      <c r="B358" t="s">
+        <v>1</v>
+      </c>
+      <c r="C358" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>1</v>
+      </c>
+      <c r="B359" t="s">
+        <v>1</v>
+      </c>
+      <c r="C359" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>1</v>
+      </c>
+      <c r="B360" t="s">
+        <v>1</v>
+      </c>
+      <c r="C360" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>1</v>
+      </c>
+      <c r="B361" t="s">
+        <v>1</v>
+      </c>
+      <c r="C361" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>1</v>
+      </c>
+      <c r="B362" t="s">
+        <v>1</v>
+      </c>
+      <c r="C362" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>1</v>
+      </c>
+      <c r="B363" t="s">
+        <v>1</v>
+      </c>
+      <c r="C363" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>1</v>
+      </c>
+      <c r="B364" t="s">
+        <v>1</v>
+      </c>
+      <c r="C364" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>1</v>
+      </c>
+      <c r="B365" t="s">
+        <v>1</v>
+      </c>
+      <c r="C365" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>1</v>
+      </c>
+      <c r="B366" t="s">
+        <v>1</v>
+      </c>
+      <c r="C366" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>1</v>
+      </c>
+      <c r="B367" t="s">
+        <v>1</v>
+      </c>
+      <c r="C367" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>1</v>
+      </c>
+      <c r="B368" t="s">
+        <v>1</v>
+      </c>
+      <c r="C368" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>1</v>
+      </c>
+      <c r="B369" t="s">
+        <v>1</v>
+      </c>
+      <c r="C369" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>1</v>
+      </c>
+      <c r="B370" t="s">
+        <v>1</v>
+      </c>
+      <c r="C370" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>1</v>
+      </c>
+      <c r="B371" t="s">
+        <v>1</v>
+      </c>
+      <c r="C371" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>1</v>
+      </c>
+      <c r="B372" t="s">
+        <v>1</v>
+      </c>
+      <c r="C372" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>1</v>
+      </c>
+      <c r="B373" t="s">
+        <v>1</v>
+      </c>
+      <c r="C373" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>1</v>
+      </c>
+      <c r="B374" t="s">
+        <v>1</v>
+      </c>
+      <c r="C374" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>1</v>
+      </c>
+      <c r="B375" t="s">
+        <v>1</v>
+      </c>
+      <c r="C375" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>1</v>
+      </c>
+      <c r="B376" t="s">
+        <v>1</v>
+      </c>
+      <c r="C376" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>1</v>
+      </c>
+      <c r="B377" t="s">
+        <v>1</v>
+      </c>
+      <c r="C377" t="s">
+        <v>567</v>
       </c>
     </row>
   </sheetData>
